--- a/sheets/S08A22P136.xlsx
+++ b/sheets/S08A22P136.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5928" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5928" uniqueCount="1570">
   <si>
     <t>Voter ID</t>
   </si>
@@ -4580,6 +4580,9 @@
   </si>
   <si>
     <t>HR/03/15/0162633</t>
+  </si>
+  <si>
+    <t>HR/03/15/0162864</t>
   </si>
   <si>
     <t>IOX1787373</t>
@@ -23700,7 +23703,7 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1127</v>
+        <v>1523</v>
       </c>
       <c r="B716" t="s">
         <v>1020</v>
@@ -23726,7 +23729,7 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B717" t="s">
         <v>1501</v>
@@ -23752,13 +23755,13 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B718" t="s">
         <v>1167</v>
       </c>
       <c r="C718" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D718" t="s">
         <v>11</v>
@@ -23778,13 +23781,13 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B719" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C719" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="D719" t="s">
         <v>11</v>
@@ -23804,10 +23807,10 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B720" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C720" t="s">
         <v>530</v>
@@ -23830,10 +23833,10 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B721" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C721" t="s">
         <v>1521</v>
@@ -23856,13 +23859,13 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B722" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C722" t="s">
         <v>1533</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C722" t="s">
-        <v>1532</v>
       </c>
       <c r="D722" t="s">
         <v>11</v>
@@ -23882,13 +23885,13 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B723" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C723" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="D723" t="s">
         <v>11</v>
@@ -23908,10 +23911,10 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B724" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C724" t="s">
         <v>160</v>
@@ -23934,13 +23937,13 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B725" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C725" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="D725" t="s">
         <v>11</v>
@@ -23960,13 +23963,13 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B726" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="C726" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D726" t="s">
         <v>11</v>
@@ -23986,7 +23989,7 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B727" t="s">
         <v>1384</v>
@@ -24012,7 +24015,7 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B728" t="s">
         <v>84</v>
@@ -24038,10 +24041,10 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B729" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C729" t="s">
         <v>1461</v>
@@ -24064,13 +24067,13 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B730" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C730" t="s">
         <v>1548</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C730" t="s">
-        <v>1547</v>
       </c>
       <c r="D730" t="s">
         <v>11</v>
@@ -24090,7 +24093,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B731" t="s">
         <v>801</v>
@@ -24116,10 +24119,10 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B732" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C732" t="s">
         <v>1461</v>
@@ -24142,13 +24145,13 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C733" t="s">
         <v>1553</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C733" t="s">
-        <v>1552</v>
       </c>
       <c r="D733" t="s">
         <v>11</v>
@@ -24168,7 +24171,7 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B734" t="s">
         <v>109</v>
@@ -24194,7 +24197,7 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B735" t="s">
         <v>817</v>
@@ -24220,7 +24223,7 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B736" t="s">
         <v>1463</v>
@@ -24246,13 +24249,13 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B737" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C737" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D737" t="s">
         <v>11</v>
@@ -24272,10 +24275,10 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B738" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="C738" t="s">
         <v>1461</v>
@@ -24298,10 +24301,10 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B739" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="C739" t="s">
         <v>326</v>
@@ -24324,13 +24327,13 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B740" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C740" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="D740" t="s">
         <v>11</v>
@@ -24350,13 +24353,13 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B741" t="s">
         <v>804</v>
       </c>
       <c r="C741" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D741" t="s">
         <v>11</v>
